--- a/important_mails_2026-05-13.xlsx
+++ b/important_mails_2026-05-13.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,21 +500,118 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 02:56:06 +0000</t>
+          <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>FBA reimbursement notification</t>
+          <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+ You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
+ Hello,
+According to rules for online stores issued by the State Council of China (Decree No. 810), we are required to provide information on China-based sellers to the Chinese tax authority on a quarterly basis.
+We’ve submitted your quarterly tax report covering October to December 2025, which includes your identity information, number of transactions, revenue, and commission and service fees.
+We’re re-sending your quarterly China tax report in case you didn’t download it in April 2026. The links below are active for seven days.
+ Download your quarterly report
+This report is provided for your reference only, no action is required.
+Based on your feedback, we’ve also provided a more granular order-level report that displays your quarterly information by transaction.
+ Download your order-level report
+ Note : Variation between the data in these reports and your payment and Amazon VAT transactions report is expected. Each report uses distinct methodology and serves a different purpose.
+We’ll continue to provide you with q</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 14:51:48 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
+ Dzień dobry,
+zgodnie z zasadami dotyczącymi sklepów internetowych wydanymi przez Radę Państwa Chin (dekret nr 810) jesteśmy zobowiązani do przekazywania informacji o sprzedawcach z siedzibą w Chinach tamtejszemu organowi podatkowemu w cyklach kwartalnych.
+Przesłaliśmy Twój kwartalny raport podatkowy za okres od października do grudnia 2025 r., który zawiera Twoje dane identyfikacyjne, liczbę transakcji, przychody oraz prowizje i opłaty za usługi.
+Ponownie wysyłamy Twój kwartalny raport podatkowy dla Chin na wypadek, gdyby nie został on pobrany w kwietniu 2026 r. Poniższe linki są aktywne przez siedem dni.
+ Pobierz raport kwartalny
+Raport ten jest przeznaczony wyłącznie do wglądu. Nie jest wymagane żadne działanie.
+Na podstawie opinii udostępniliśmy również bardziej szczegółowy raport na poziomie zamówienia, który przedstawia informacje kwartalne z podziałem na transakcje.
+ Pobierz raport z informacjami na poziomie zamówienia
+ Uwaga: Mogą wystąpić różnice między danymi w tych raportach a raportem o płatnościach </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 02:56:06 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -530,39 +627,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -587,39 +684,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -639,39 +736,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -691,39 +788,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -743,39 +840,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -796,39 +893,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -845,39 +942,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -897,39 +994,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -949,40 +1046,40 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -997,40 +1094,40 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1044,40 +1141,40 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1091,41 +1188,41 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -1136,39 +1233,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 10:10:51 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>EPR Pay on Behalf charges for 2024 Amazon.co.uk sales</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1187,39 +1284,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 12:21:34 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -1241,39 +1338,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:22:50 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1295,39 +1392,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 16:23:48 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -1346,39 +1443,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 08:34:05 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1390,39 +1487,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:22:14 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1434,39 +1531,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:02:56 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
@@ -1478,39 +1575,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:29:17 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1522,39 +1619,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:25:39 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1566,39 +1663,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:10:57 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1610,39 +1707,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:09:44 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1661,39 +1758,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:01:18 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1712,39 +1809,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:25:07 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 4 2026</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 4 i rok 2026.
@@ -1756,39 +1853,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:24:35 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -1800,39 +1897,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:03:04 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1844,39 +1941,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 20:51:50 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1888,39 +1985,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:44:14 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 4 2026</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 4 i rok 2026.
@@ -1932,39 +2029,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:35:59 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1976,39 +2073,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:24:07 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2020,39 +2117,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:18:06 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2064,39 +2161,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:33:15 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2108,39 +2205,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:20:52 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2152,39 +2249,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:43:38 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2196,39 +2293,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:17:48 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2240,39 +2337,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:52:53 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2284,40 +2381,40 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:40:42 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2336,39 +2433,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:57:28 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2380,39 +2477,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:43:13 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2424,39 +2521,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:40:52 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2468,39 +2565,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:55:06 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2512,39 +2609,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:49:29 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2556,39 +2653,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:20:15 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -2606,104 +2703,6 @@
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
  -4 % 20,15 € UVP: 20,97 €
 https://www.amazon.de/gp/product/B0CSGBZG8W/?ref_=ci_mc</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 6 May 2026 15:00:42 +0000</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Votre paiement est en cours</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Félicitations ! Votre paiement est en cours et arrivera sous peu.
- Tentative de versement
-Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
-Le 05/06/26 15:00 CEST, nous avons effectué un virement d’un montant de €
- 110.91 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
- Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
- Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
- Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de p</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 6 May 2026 14:24:59 +0000</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.ae
- عزيزي Shen zhen shi wei hai zhong xin ke ji you xian،
-نراسلك لإبلاغك بأن فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاص بك لشهر 4/2026 متاح الآن في حساب Seller Central الخاص بك.
-للوصول إلى فاتورة الخاص بك، انتقل إلى حساب Seller Central الخاص بك &gt; التقارير &gt; مكتبة المستندات الضريبية &gt; فواتير ضريبة رسم البائع.
-في حساب Seller Central الخاص بك، ستتمكن من عرض {documentType}$ الخاص بك أو تنزيله أو طباعته.
-إذا كانت لديك أي أسئلة، فالمرجو التواصل مع دعم البائع.
- مع أطيب التحيات،
-Amazon.ae</t>
         </is>
       </c>
     </row>
@@ -5844,21 +5843,119 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Sun, 3 May 2026 05:32:15 +0000</t>
+          <t>Wed, 6 May 2026 15:00:42 +0000</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Dein Einkaufswagen wartet</t>
+          <t>Votre paiement est en cours</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Félicitations ! Votre paiement est en cours et arrivera sous peu.
+ Tentative de versement
+Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
+Le 05/06/26 15:00 CEST, nous avons effectué un virement d’un montant de €
+ 110.91 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
+ Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
+ Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
+ Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de p</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 6 May 2026 14:24:59 +0000</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.ae
+ عزيزي Shen zhen shi wei hai zhong xin ke ji you xian،
+نراسلك لإبلاغك بأن فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاص بك لشهر 4/2026 متاح الآن في حساب Seller Central الخاص بك.
+للوصول إلى فاتورة الخاص بك، انتقل إلى حساب Seller Central الخاص بك &gt; التقارير &gt; مكتبة المستندات الضريبية &gt; فواتير ضريبة رسم البائع.
+في حساب Seller Central الخاص بك، ستتمكن من عرض {documentType}$ الخاص بك أو تنزيله أو طباعته.
+إذا كانت لديك أي أسئلة، فالمرجو التواصل مع دعم البائع.
+ مع أطيب التحيات،
+Amazon.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 3 May 2026 05:32:15 +0000</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Dein Einkaufswagen wartet</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -5880,39 +5977,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:27:47 +0600</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Rating Deals</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Not getting sales on Amazon? Even after doing everything right? Then this
 message is for you!
@@ -5938,40 +6035,40 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5987,40 +6084,40 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6036,39 +6133,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6084,39 +6181,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6132,39 +6229,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 15:09:15 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6180,39 +6277,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:16:19 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6226,39 +6323,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -6276,40 +6373,40 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6325,39 +6422,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6373,39 +6470,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6421,40 +6518,40 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6470,39 +6567,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -6519,39 +6616,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -6580,39 +6677,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6628,39 +6725,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6674,39 +6771,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6721,39 +6818,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -6773,39 +6870,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -6834,40 +6931,40 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -6880,39 +6977,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -6927,39 +7024,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -6972,40 +7069,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -7020,40 +7117,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -7067,39 +7164,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -7113,39 +7210,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -7160,39 +7257,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -7206,39 +7303,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -7253,39 +7350,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7300,39 +7397,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7351,39 +7448,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -7399,39 +7496,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -7452,39 +7549,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7502,40 +7599,40 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7553,39 +7650,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7602,39 +7699,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -7652,40 +7749,40 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7703,39 +7800,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7753,39 +7850,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -7802,39 +7899,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7849,39 +7946,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7900,39 +7997,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -7950,39 +8047,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -8021,39 +8118,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -8069,40 +8166,40 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -8118,39 +8215,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -8166,39 +8263,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -8212,40 +8309,40 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -8261,39 +8358,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -8309,39 +8406,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -8362,39 +8459,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8409,39 +8506,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -8458,39 +8555,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -8504,39 +8601,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -8555,40 +8652,40 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -8602,39 +8699,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8658,39 +8755,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8714,39 +8811,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8767,39 +8864,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8821,39 +8918,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8876,39 +8973,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8929,39 +9026,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8984,39 +9081,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -9046,39 +9143,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -9127,39 +9224,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -9168,39 +9265,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.

--- a/important_mails_2026-05-13.xlsx
+++ b/important_mails_2026-05-13.xlsx
@@ -549,21 +549,81 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 14:51:48 +0000</t>
+          <t>Wed, 13 May 2026 16:40:18 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
+          <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Hola Weihai EU,
+Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
+Nuestro equipo de
+análisis ha señalado que una asociación con usted sería una gran oportunidad
+para ambos.
+¿Estaría
+disponible para una reunión online esta semana?
+Acerca de Worten
+- Somos el líder del mercado portugués:
+- Nº 1 del
+comercio electrónico portugués
+- Sitio web con
+mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
+- Más de 200
+tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
+- Plataforma de
+gestión: Mirakl (se puede integrar manualmente o vía API)
+- Sin costes los 6 meses iniciales
+Estaré encantado
+de ayudarle si tiene alguna pregunta.
+Muchas gracias,
+Saludos
+Cordiales</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 14:51:48 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -579,39 +639,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -627,39 +687,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -684,39 +744,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -736,39 +796,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -788,39 +848,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -837,59 +897,6 @@
 ------------------------------------------------------------------------------
 Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
 SPC-EUAmazon-756465651024921</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 6 May 2026 16:07:01 +0000</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID ZazNpo+O9J
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on May 20, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-897203698552067</t>
         </is>
       </c>
     </row>
@@ -2876,21 +2883,74 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Tue, 5 May 2026 13:03:07 +0000</t>
+          <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (2604121A02)</t>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID ZazNpo+O9J
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on May 20, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-897203698552067</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 5 May 2026 13:03:07 +0000</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (2604121A02)</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2910,39 +2970,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2962,39 +3022,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -3010,39 +3070,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3062,39 +3122,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -3110,39 +3170,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3162,39 +3222,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3211,39 +3271,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -3258,39 +3318,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3306,39 +3366,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3358,39 +3418,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3410,39 +3470,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3459,39 +3519,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3511,39 +3571,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3563,39 +3623,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3612,39 +3672,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3664,39 +3724,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -3710,39 +3770,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3762,39 +3822,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3811,39 +3871,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3859,39 +3919,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3911,39 +3971,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3960,39 +4020,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -4001,61 +4061,6 @@
  Vous pouvez consulter votre solde à tout moment en vous connectant à la section Rapport sur les paiements de votre compte.
  Merci de vendre sur Amazon.
 Amazon Payments Europe SCA (société en commandite par actions) est immatriculée au Registre de Commerce et des Sociétés de Luxembourg (n° 153 265) et sise 38, avenue John F. Kennedy, L-1855 Luxembourg. Numéro de TVA : LU 24448288. Amazon Payments Europe SCA est autorisée par la Commission de Surveillance du Secteur Financier en tant qu’établissement de monnaie électronique (licence n° 36/10). Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>Negative balance adjustment across your Selling on Amazon accounts</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- We’ve adjusted your negative balance of €261.54 that was due from your Amazon.fr seller account on April 13, 2026, with funds that were available in your Amazon.be, Amazon.es, Amazon.nl accounts. You can view your account balance at any time by logging into your account and navigating to the Payments dashboard .
-For more information, go to Negative balance adjustment across your accounts .
-Regards,
-Amazon Payments Europe
- Report an issue with this email
- If you have any questions, visit: Seller Central
- To change your email preferences, visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon Payments Europe
- 38 avenue John F. Kennedy,
- L-1855 Luxembourg, Registered in Luxembourg No. B-101818,
- Share Capital 165.833 EUR,
- Business License Number: 134248,
- Luxembourg VAT Reg. No. LU 20260743.
- This email is sent from an unmonitored email address.
- SPC-EUAmazon-439806292595808</t>
         </is>
       </c>
     </row>
